--- a/public/prices/2026-09-25-zilma-price.xlsx
+++ b/public/prices/2026-09-25-zilma-price.xlsx
@@ -1514,7 +1514,7 @@
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Лосьон д/удаления краски с кожи головы 200млголовы c/sl</t>
+          <t>Лосьон для удаления краски с кожи головы 200мл c/sl</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -1537,7 +1537,7 @@
     <row r="35">
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Эмульсия д/удаления краски с волос 3шт*100мл COLOR OFF c/f</t>
+          <t>Эмульсия для удаления краски с волос COLOR OFF 3шт*100мл c/f</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
